--- a/models.xlsx
+++ b/models.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthurde/LSCMR/6MWT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F59D885F-3A7B-574D-9599-275401E5F4DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B507BC6-C879-544E-A3CC-D26903A2F018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="660" windowWidth="29360" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="123">
   <si>
     <t>Poh et. al 2006</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>∆FC</t>
+  </si>
+  <si>
+    <t>Corridor lenght</t>
   </si>
 </sst>
 </file>
@@ -446,12 +449,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -475,7 +484,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -538,6 +547,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BY26"/>
+  <dimension ref="A1:BX27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.5" style="6" bestFit="1" customWidth="1"/>
@@ -788,12 +812,12 @@
     <col min="58" max="59" width="32.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="60" max="61" width="28.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="62" max="63" width="28.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="64" max="72" width="10.6640625" style="6" customWidth="1"/>
-    <col min="73" max="77" width="11.1640625" style="6" customWidth="1"/>
-    <col min="78" max="16384" width="11.1640625" style="6"/>
+    <col min="64" max="71" width="10.6640625" style="6" customWidth="1"/>
+    <col min="72" max="76" width="11.1640625" style="6" customWidth="1"/>
+    <col min="77" max="16384" width="11.1640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:76" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>67</v>
       </c>
@@ -985,7 +1009,7 @@
       </c>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
-      <c r="BN1" s="1"/>
+      <c r="BN1" s="4"/>
       <c r="BO1" s="4"/>
       <c r="BP1" s="4"/>
       <c r="BQ1" s="4"/>
@@ -996,9 +1020,8 @@
       <c r="BV1" s="4"/>
       <c r="BW1" s="4"/>
       <c r="BX1" s="4"/>
-      <c r="BY1" s="4"/>
     </row>
-    <row r="2" spans="1:77" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:76" s="7" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -1182,7 +1205,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
@@ -1357,7 +1380,7 @@
       </c>
       <c r="BL3" s="11"/>
       <c r="BM3" s="11"/>
-      <c r="BN3" s="11"/>
+      <c r="BN3" s="12"/>
       <c r="BO3" s="12"/>
       <c r="BP3" s="12"/>
       <c r="BQ3" s="12"/>
@@ -1368,9 +1391,8 @@
       <c r="BV3" s="12"/>
       <c r="BW3" s="12"/>
       <c r="BX3" s="12"/>
-      <c r="BY3" s="12"/>
     </row>
-    <row r="4" spans="1:77" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:76" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1448,7 +1470,7 @@
       <c r="BK4" s="15"/>
       <c r="BL4" s="15"/>
       <c r="BM4" s="15"/>
-      <c r="BN4" s="15"/>
+      <c r="BN4" s="16"/>
       <c r="BO4" s="16"/>
       <c r="BP4" s="16"/>
       <c r="BQ4" s="16"/>
@@ -1459,9 +1481,8 @@
       <c r="BV4" s="16"/>
       <c r="BW4" s="16"/>
       <c r="BX4" s="16"/>
-      <c r="BY4" s="16"/>
     </row>
-    <row r="5" spans="1:77" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:76" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>34</v>
       </c>
@@ -1646,7 +1667,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="6" spans="1:77" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:76" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>88</v>
       </c>
@@ -1825,7 +1846,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:77" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:76" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>119</v>
       </c>
@@ -1938,425 +1959,410 @@
       </c>
       <c r="BK7" s="19"/>
     </row>
-    <row r="8" spans="1:77" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:76" s="25" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="24">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
+        <f>100*0.3048</f>
+        <v>30.48</v>
+      </c>
+      <c r="BH8" s="26"/>
+      <c r="BK8" s="26"/>
+    </row>
+    <row r="9" spans="1:76" s="13" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="15" t="s">
+      <c r="D9" s="14"/>
+      <c r="E9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J9" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L9" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="O8" s="15" t="s">
+      <c r="O9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="15" t="s">
+      <c r="P9" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="R8" s="15" t="s">
+      <c r="R9" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="S8" s="15" t="s">
+      <c r="S9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="T8" s="15" t="s">
+      <c r="T9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="U8" s="15" t="s">
+      <c r="U9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="V8" s="15" t="s">
+      <c r="V9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="W8" s="15" t="s">
+      <c r="W9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="X8" s="15" t="s">
+      <c r="X9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Y8" s="15" t="s">
+      <c r="Y9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Z8" s="15" t="s">
+      <c r="Z9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AA8" s="15" t="s">
+      <c r="AA9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AB8" s="15" t="s">
+      <c r="AB9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AC8" s="15" t="s">
+      <c r="AC9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AD8" s="15" t="s">
+      <c r="AD9" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="AE8" s="15" t="s">
+      <c r="AE9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AF8" s="15" t="s">
+      <c r="AF9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="AG8" s="15" t="s">
+      <c r="AG9" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="AH8" s="15" t="s">
+      <c r="AH9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AI8" s="15" t="s">
+      <c r="AI9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="AJ8" s="15" t="s">
+      <c r="AJ9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AK8" s="15" t="s">
+      <c r="AK9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AL8" s="15" t="s">
+      <c r="AL9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AM8" s="15" t="s">
+      <c r="AM9" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AN8" s="15" t="s">
+      <c r="AN9" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AO8" s="15" t="s">
+      <c r="AO9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="AP8" s="15" t="s">
+      <c r="AP9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="AQ8" s="15" t="s">
+      <c r="AQ9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AR8" s="15" t="s">
+      <c r="AR9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AS8" s="15" t="s">
+      <c r="AS9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AT8" s="15" t="s">
+      <c r="AT9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AU8" s="15" t="s">
+      <c r="AU9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AV8" s="15" t="s">
+      <c r="AV9" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="AW8" s="15" t="s">
+      <c r="AW9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="AX8" s="15" t="s">
+      <c r="AX9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="AY8" s="15" t="s">
+      <c r="AY9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="AZ8" s="15" t="s">
+      <c r="AZ9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="BA8" s="15" t="s">
+      <c r="BA9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="BB8" s="15" t="s">
+      <c r="BB9" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="BC8" s="15" t="s">
+      <c r="BC9" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="BD8" s="15" t="s">
+      <c r="BD9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="BE8" s="15" t="s">
+      <c r="BE9" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="BF8" s="15" t="s">
+      <c r="BF9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="BG8" s="15" t="s">
+      <c r="BG9" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="BH8" s="15" t="s">
+      <c r="BH9" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="BI8" s="15" t="s">
+      <c r="BI9" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="BJ8" s="15" t="s">
+      <c r="BJ9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="BK8" s="15" t="s">
+      <c r="BK9" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="BL8" s="15"/>
-      <c r="BM8" s="15"/>
-      <c r="BN8" s="15"/>
-      <c r="BO8" s="16"/>
-      <c r="BP8" s="16"/>
-      <c r="BQ8" s="16"/>
-      <c r="BR8" s="16"/>
-      <c r="BS8" s="16"/>
-      <c r="BT8" s="16"/>
-      <c r="BU8" s="16"/>
-      <c r="BV8" s="16"/>
-      <c r="BW8" s="16"/>
-      <c r="BX8" s="16"/>
-      <c r="BY8" s="16"/>
+      <c r="BL9" s="15"/>
+      <c r="BM9" s="15"/>
+      <c r="BN9" s="16"/>
+      <c r="BO9" s="16"/>
+      <c r="BP9" s="16"/>
+      <c r="BQ9" s="16"/>
+      <c r="BR9" s="16"/>
+      <c r="BS9" s="16"/>
+      <c r="BT9" s="16"/>
+      <c r="BU9" s="16"/>
+      <c r="BV9" s="16"/>
+      <c r="BW9" s="16"/>
+      <c r="BX9" s="16"/>
     </row>
-    <row r="9" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+    <row r="10" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7">
-        <v>1</v>
-      </c>
-      <c r="E9" s="12">
-        <v>-309</v>
-      </c>
-      <c r="F9" s="12">
-        <v>667</v>
-      </c>
-      <c r="G9" s="12">
-        <v>218</v>
-      </c>
-      <c r="H9" s="12">
-        <v>218</v>
-      </c>
-      <c r="I9" s="12">
-        <v>868.8</v>
-      </c>
-      <c r="J9" s="12">
-        <v>868.8</v>
-      </c>
-      <c r="K9" s="12">
-        <v>493</v>
-      </c>
-      <c r="L9" s="12">
-        <v>410</v>
-      </c>
-      <c r="M9" s="12">
-        <v>64.69</v>
-      </c>
-      <c r="N9" s="12">
-        <v>216.9</v>
-      </c>
-      <c r="O9" s="12">
-        <v>216.9</v>
-      </c>
-      <c r="P9" s="12">
-        <v>-473.27</v>
-      </c>
-      <c r="Q9" s="12">
-        <v>518.85299999999995</v>
-      </c>
-      <c r="R9" s="12">
-        <v>518.85299999999995</v>
-      </c>
-      <c r="S9" s="12">
-        <v>299.8</v>
-      </c>
-      <c r="T9" s="12">
-        <v>299.8</v>
-      </c>
-      <c r="U9" s="12">
-        <v>622.46100000000001</v>
-      </c>
-      <c r="V9" s="12">
-        <v>622.46100000000001</v>
-      </c>
-      <c r="W9" s="12">
-        <v>1005</v>
-      </c>
-      <c r="X9" s="12">
-        <v>602</v>
-      </c>
-      <c r="Y9" s="12">
-        <v>849</v>
-      </c>
-      <c r="Z9" s="12">
-        <v>594</v>
-      </c>
-      <c r="AA9" s="12">
-        <v>748</v>
-      </c>
-      <c r="AB9" s="12">
-        <v>541</v>
-      </c>
-      <c r="AC9" s="12">
-        <v>867</v>
-      </c>
-      <c r="AD9" s="12">
-        <v>525</v>
-      </c>
-      <c r="AE9" s="12">
-        <v>-28.5</v>
-      </c>
-      <c r="AF9" s="12">
-        <v>720.5</v>
-      </c>
-      <c r="AG9" s="12">
-        <v>720.5</v>
-      </c>
-      <c r="AH9" s="12">
-        <v>457</v>
-      </c>
-      <c r="AI9" s="12">
-        <v>530</v>
-      </c>
-      <c r="AJ9" s="12">
-        <v>511</v>
-      </c>
-      <c r="AK9" s="12">
-        <v>299.29599999999999</v>
-      </c>
-      <c r="AL9" s="12">
-        <v>299.29599999999999</v>
-      </c>
-      <c r="AM9" s="12">
-        <v>361</v>
-      </c>
-      <c r="AN9" s="12">
-        <v>361</v>
-      </c>
-      <c r="AO9" s="12">
-        <v>970.7</v>
-      </c>
-      <c r="AP9" s="12">
-        <v>970.7</v>
-      </c>
-      <c r="AQ9" s="12">
-        <v>890.46</v>
-      </c>
-      <c r="AR9" s="12">
-        <v>890.46</v>
-      </c>
-      <c r="AS9" s="12">
-        <v>356.65800000000002</v>
-      </c>
-      <c r="AT9" s="12">
-        <v>356.65800000000002</v>
-      </c>
-      <c r="AU9" s="12">
-        <v>164.08</v>
-      </c>
-      <c r="AV9" s="12">
-        <v>164.08</v>
-      </c>
-      <c r="AW9" s="12">
-        <v>105.7</v>
-      </c>
-      <c r="AX9" s="12">
-        <v>586.25400000000002</v>
-      </c>
-      <c r="AY9" s="12">
-        <v>586.25400000000002</v>
-      </c>
-      <c r="AZ9" s="12">
-        <v>553.28899999999999</v>
-      </c>
-      <c r="BA9" s="12">
-        <v>553.28899999999999</v>
-      </c>
-      <c r="BB9" s="12">
-        <v>233.994</v>
-      </c>
-      <c r="BC9" s="12">
-        <v>141.327</v>
-      </c>
-      <c r="BD9" s="12">
-        <v>787.18700000000001</v>
-      </c>
-      <c r="BE9" s="12">
-        <v>721.75300000000004</v>
-      </c>
-      <c r="BF9" s="12">
-        <v>910.1</v>
-      </c>
-      <c r="BG9" s="12">
-        <v>778.1</v>
-      </c>
-      <c r="BH9" s="12">
-        <v>-185.34100000000001</v>
-      </c>
-      <c r="BI9" s="12">
-        <v>-185.43100000000001</v>
-      </c>
-      <c r="BJ9" s="12">
-        <v>498.06</v>
-      </c>
-      <c r="BK9" s="12">
-        <v>489.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>61</v>
-      </c>
+      <c r="C10" s="6"/>
       <c r="D10" s="7">
         <v>1</v>
       </c>
+      <c r="E10" s="12">
+        <v>-309</v>
+      </c>
+      <c r="F10" s="12">
+        <v>667</v>
+      </c>
+      <c r="G10" s="12">
+        <v>218</v>
+      </c>
+      <c r="H10" s="12">
+        <v>218</v>
+      </c>
+      <c r="I10" s="12">
+        <v>868.8</v>
+      </c>
+      <c r="J10" s="12">
+        <v>868.8</v>
+      </c>
+      <c r="K10" s="12">
+        <v>493</v>
+      </c>
+      <c r="L10" s="12">
+        <v>410</v>
+      </c>
+      <c r="M10" s="12">
+        <v>64.69</v>
+      </c>
+      <c r="N10" s="12">
+        <v>216.9</v>
+      </c>
+      <c r="O10" s="12">
+        <v>216.9</v>
+      </c>
+      <c r="P10" s="12">
+        <v>-473.27</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>518.85299999999995</v>
+      </c>
+      <c r="R10" s="12">
+        <v>518.85299999999995</v>
+      </c>
       <c r="S10" s="12">
-        <v>342.6</v>
+        <v>299.8</v>
       </c>
       <c r="T10" s="12">
-        <v>342.6</v>
+        <v>299.8</v>
+      </c>
+      <c r="U10" s="12">
+        <v>622.46100000000001</v>
+      </c>
+      <c r="V10" s="12">
+        <v>622.46100000000001</v>
+      </c>
+      <c r="W10" s="12">
+        <v>1005</v>
+      </c>
+      <c r="X10" s="12">
+        <v>602</v>
+      </c>
+      <c r="Y10" s="12">
+        <v>849</v>
+      </c>
+      <c r="Z10" s="12">
+        <v>594</v>
+      </c>
+      <c r="AA10" s="12">
+        <v>748</v>
+      </c>
+      <c r="AB10" s="12">
+        <v>541</v>
+      </c>
+      <c r="AC10" s="12">
+        <v>867</v>
+      </c>
+      <c r="AD10" s="12">
+        <v>525</v>
+      </c>
+      <c r="AE10" s="12">
+        <v>-28.5</v>
+      </c>
+      <c r="AF10" s="12">
+        <v>720.5</v>
+      </c>
+      <c r="AG10" s="12">
+        <v>720.5</v>
+      </c>
+      <c r="AH10" s="12">
+        <v>457</v>
+      </c>
+      <c r="AI10" s="12">
+        <v>530</v>
+      </c>
+      <c r="AJ10" s="12">
+        <v>511</v>
       </c>
       <c r="AK10" s="12">
-        <v>361.73099999999999</v>
+        <v>299.29599999999999</v>
       </c>
       <c r="AL10" s="12">
-        <v>361.73099999999999</v>
+        <v>299.29599999999999</v>
+      </c>
+      <c r="AM10" s="12">
+        <v>361</v>
+      </c>
+      <c r="AN10" s="12">
+        <v>361</v>
+      </c>
+      <c r="AO10" s="12">
+        <v>970.7</v>
+      </c>
+      <c r="AP10" s="12">
+        <v>970.7</v>
+      </c>
+      <c r="AQ10" s="12">
+        <v>890.46</v>
+      </c>
+      <c r="AR10" s="12">
+        <v>890.46</v>
+      </c>
+      <c r="AS10" s="12">
+        <v>356.65800000000002</v>
+      </c>
+      <c r="AT10" s="12">
+        <v>356.65800000000002</v>
+      </c>
+      <c r="AU10" s="12">
+        <v>164.08</v>
+      </c>
+      <c r="AV10" s="12">
+        <v>164.08</v>
+      </c>
+      <c r="AW10" s="12">
+        <v>105.7</v>
+      </c>
+      <c r="AX10" s="12">
+        <v>586.25400000000002</v>
+      </c>
+      <c r="AY10" s="12">
+        <v>586.25400000000002</v>
+      </c>
+      <c r="AZ10" s="12">
+        <v>553.28899999999999</v>
+      </c>
+      <c r="BA10" s="12">
+        <v>553.28899999999999</v>
+      </c>
+      <c r="BB10" s="12">
+        <v>233.994</v>
+      </c>
+      <c r="BC10" s="12">
+        <v>141.327</v>
+      </c>
+      <c r="BD10" s="12">
+        <v>787.18700000000001</v>
+      </c>
+      <c r="BE10" s="12">
+        <v>721.75300000000004</v>
+      </c>
+      <c r="BF10" s="12">
+        <v>910.1</v>
+      </c>
+      <c r="BG10" s="12">
+        <v>778.1</v>
       </c>
       <c r="BH10" s="12">
-        <v>288.28199999999998</v>
+        <v>-185.34100000000001</v>
       </c>
       <c r="BI10" s="12">
-        <v>288.28199999999998</v>
+        <v>-185.43100000000001</v>
+      </c>
+      <c r="BJ10" s="12">
+        <v>498.06</v>
+      </c>
+      <c r="BK10" s="12">
+        <v>489.22</v>
       </c>
     </row>
-    <row r="11" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
         <v>69</v>
       </c>
@@ -2364,127 +2370,31 @@
         <v>70</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="7">
         <v>1</v>
       </c>
-      <c r="E11" s="12">
-        <v>7.57</v>
-      </c>
-      <c r="F11" s="12">
-        <v>2.11</v>
-      </c>
-      <c r="G11" s="12">
-        <v>5.14</v>
-      </c>
-      <c r="H11" s="12">
-        <v>5.14</v>
-      </c>
-      <c r="K11" s="12">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="L11" s="12">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="M11" s="12">
-        <v>3.12</v>
-      </c>
-      <c r="N11" s="12">
-        <v>4.12</v>
-      </c>
-      <c r="O11" s="12">
-        <v>4.12</v>
-      </c>
-      <c r="P11" s="12">
-        <v>6.94</v>
-      </c>
-      <c r="Q11" s="12">
-        <v>1.25</v>
-      </c>
-      <c r="R11" s="12">
-        <v>1.25</v>
-      </c>
-      <c r="W11" s="12">
-        <v>0.89</v>
-      </c>
-      <c r="X11" s="12">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="Y11" s="12">
-        <v>0.22</v>
-      </c>
-      <c r="Z11" s="12">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>0.64</v>
-      </c>
-      <c r="AB11" s="12">
-        <v>1.8</v>
-      </c>
-      <c r="AC11" s="12">
-        <v>1.03</v>
-      </c>
-      <c r="AD11" s="12">
-        <v>2.71</v>
-      </c>
-      <c r="AE11" s="12">
-        <v>2.81</v>
-      </c>
-      <c r="AF11" s="12">
-        <v>2.72</v>
-      </c>
-      <c r="AG11" s="12">
-        <v>2.72</v>
-      </c>
-      <c r="AH11" s="12">
-        <v>2.61</v>
-      </c>
-      <c r="AI11" s="12">
-        <v>2.36</v>
-      </c>
-      <c r="AM11" s="12">
-        <v>2</v>
-      </c>
-      <c r="AN11" s="12">
-        <v>2</v>
-      </c>
-      <c r="AS11" s="12">
-        <v>1.704</v>
-      </c>
-      <c r="AT11" s="12">
-        <v>1.704</v>
-      </c>
-      <c r="AU11" s="12">
-        <v>1.95</v>
-      </c>
-      <c r="AV11" s="12">
-        <v>1.95</v>
-      </c>
-      <c r="AW11" s="12">
-        <v>2.99</v>
-      </c>
-      <c r="AX11" s="12">
-        <v>-0.26500000000000001</v>
-      </c>
-      <c r="AY11" s="12">
-        <v>-0.26500000000000001</v>
-      </c>
-      <c r="BB11" s="12">
-        <v>2.6320000000000001</v>
-      </c>
-      <c r="BC11" s="12">
-        <v>3.0379999999999998</v>
-      </c>
-      <c r="BJ11" s="12">
-        <v>2.64</v>
-      </c>
-      <c r="BK11" s="12">
-        <v>3.19</v>
+      <c r="S11" s="12">
+        <v>342.6</v>
+      </c>
+      <c r="T11" s="12">
+        <v>342.6</v>
+      </c>
+      <c r="AK11" s="12">
+        <v>361.73099999999999</v>
+      </c>
+      <c r="AL11" s="12">
+        <v>361.73099999999999</v>
+      </c>
+      <c r="BH11" s="12">
+        <v>288.28199999999998</v>
+      </c>
+      <c r="BI11" s="12">
+        <v>288.28199999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>69</v>
       </c>
@@ -2495,36 +2405,141 @@
         <v>62</v>
       </c>
       <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="12">
+        <v>7.57</v>
+      </c>
+      <c r="F12" s="12">
+        <v>2.11</v>
+      </c>
+      <c r="G12" s="12">
+        <v>5.14</v>
+      </c>
+      <c r="H12" s="12">
+        <v>5.14</v>
+      </c>
+      <c r="K12" s="12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L12" s="12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M12" s="12">
+        <v>3.12</v>
+      </c>
+      <c r="N12" s="12">
+        <v>4.12</v>
+      </c>
+      <c r="O12" s="12">
+        <v>4.12</v>
+      </c>
+      <c r="P12" s="12">
+        <v>6.94</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>1.25</v>
+      </c>
+      <c r="R12" s="12">
+        <v>1.25</v>
+      </c>
+      <c r="W12" s="12">
+        <v>0.89</v>
+      </c>
+      <c r="X12" s="12">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="Y12" s="12">
+        <v>0.22</v>
+      </c>
+      <c r="Z12" s="12">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="AA12" s="12">
+        <v>0.64</v>
+      </c>
+      <c r="AB12" s="12">
+        <v>1.8</v>
+      </c>
+      <c r="AC12" s="12">
+        <v>1.03</v>
+      </c>
+      <c r="AD12" s="12">
+        <v>2.71</v>
+      </c>
+      <c r="AE12" s="12">
+        <v>2.81</v>
+      </c>
+      <c r="AF12" s="12">
+        <v>2.72</v>
+      </c>
+      <c r="AG12" s="12">
+        <v>2.72</v>
+      </c>
+      <c r="AH12" s="12">
+        <v>2.61</v>
+      </c>
+      <c r="AI12" s="12">
+        <v>2.36</v>
+      </c>
+      <c r="AM12" s="12">
         <v>2</v>
       </c>
-      <c r="AJ12" s="12">
-        <v>6.6E-3</v>
+      <c r="AN12" s="12">
+        <v>2</v>
+      </c>
+      <c r="AS12" s="12">
+        <v>1.704</v>
+      </c>
+      <c r="AT12" s="12">
+        <v>1.704</v>
+      </c>
+      <c r="AU12" s="12">
+        <v>1.95</v>
+      </c>
+      <c r="AV12" s="12">
+        <v>1.95</v>
+      </c>
+      <c r="AW12" s="12">
+        <v>2.99</v>
+      </c>
+      <c r="AX12" s="12">
+        <v>-0.26500000000000001</v>
+      </c>
+      <c r="AY12" s="12">
+        <v>-0.26500000000000001</v>
+      </c>
+      <c r="BB12" s="12">
+        <v>2.6320000000000001</v>
+      </c>
+      <c r="BC12" s="12">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="BJ12" s="12">
+        <v>2.64</v>
+      </c>
+      <c r="BK12" s="12">
+        <v>3.19</v>
       </c>
     </row>
-    <row r="13" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D13" s="7">
         <v>2</v>
       </c>
       <c r="AJ13" s="12">
-        <v>-0.03</v>
-      </c>
-      <c r="AQ13" s="12">
-        <v>3.4500000000000003E-2</v>
-      </c>
-      <c r="AR13" s="12">
-        <v>3.4500000000000003E-2</v>
+        <v>6.6E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>71</v>
       </c>
@@ -2535,172 +2550,19 @@
         <v>63</v>
       </c>
       <c r="D14" s="7">
-        <v>1</v>
-      </c>
-      <c r="E14" s="12">
-        <v>-5.0199999999999996</v>
-      </c>
-      <c r="F14" s="12">
-        <v>-5.78</v>
-      </c>
-      <c r="G14" s="12">
-        <v>-5.32</v>
-      </c>
-      <c r="H14" s="12">
-        <v>-5.32</v>
-      </c>
-      <c r="I14" s="12">
-        <v>-2.99</v>
-      </c>
-      <c r="J14" s="12">
-        <v>-2.99</v>
-      </c>
-      <c r="K14" s="12">
-        <v>-5.3</v>
-      </c>
-      <c r="L14" s="12">
-        <v>-5.3</v>
-      </c>
-      <c r="N14" s="12">
-        <v>-1.75</v>
-      </c>
-      <c r="O14" s="12">
-        <v>-1.75</v>
-      </c>
-      <c r="P14" s="12">
-        <v>-4.49</v>
-      </c>
-      <c r="Q14" s="12">
-        <v>-2.8159999999999998</v>
-      </c>
-      <c r="R14" s="12">
-        <v>-2.8159999999999998</v>
-      </c>
-      <c r="S14" s="12">
-        <v>-4.34</v>
-      </c>
-      <c r="T14" s="12">
-        <v>-4.34</v>
-      </c>
-      <c r="U14" s="12">
-        <v>-1.8460000000000001</v>
-      </c>
-      <c r="V14" s="12">
-        <v>-1.8460000000000001</v>
-      </c>
-      <c r="W14" s="12">
-        <v>-5.68</v>
-      </c>
-      <c r="X14" s="12">
-        <v>-2.97</v>
-      </c>
-      <c r="Y14" s="12">
-        <v>-6.15</v>
-      </c>
-      <c r="Z14" s="12">
-        <v>-3.95</v>
-      </c>
-      <c r="AA14" s="12">
-        <v>-6.32</v>
-      </c>
-      <c r="AB14" s="12">
-        <v>-3.81</v>
-      </c>
-      <c r="AC14" s="12">
-        <v>-5.71</v>
-      </c>
-      <c r="AD14" s="12">
-        <v>-2.86</v>
-      </c>
-      <c r="AE14" s="12">
-        <v>0.79</v>
-      </c>
-      <c r="AF14" s="12">
-        <v>-5.14</v>
-      </c>
-      <c r="AG14" s="12">
-        <v>-5.14</v>
-      </c>
-      <c r="AH14" s="12">
-        <v>-3.46</v>
-      </c>
-      <c r="AI14" s="12">
-        <v>-3.31</v>
-      </c>
-      <c r="AK14" s="12">
-        <v>-2.7280000000000002</v>
-      </c>
-      <c r="AL14" s="12">
-        <v>-2.7280000000000002</v>
-      </c>
-      <c r="AM14" s="12">
-        <v>-4</v>
-      </c>
-      <c r="AN14" s="12">
-        <v>-4</v>
-      </c>
-      <c r="AO14" s="12">
-        <v>-5.5</v>
-      </c>
-      <c r="AP14" s="12">
-        <v>-5.5</v>
+        <v>2</v>
+      </c>
+      <c r="AJ14" s="12">
+        <v>-0.03</v>
       </c>
       <c r="AQ14" s="12">
-        <v>-6.11</v>
+        <v>3.4500000000000003E-2</v>
       </c>
       <c r="AR14" s="12">
-        <v>-6.11</v>
-      </c>
-      <c r="AS14" s="12">
-        <v>-2.3029999999999999</v>
-      </c>
-      <c r="AT14" s="12">
-        <v>-2.3029999999999999</v>
-      </c>
-      <c r="AU14" s="12">
-        <v>-1.9</v>
-      </c>
-      <c r="AV14" s="12">
-        <v>-1.9</v>
-      </c>
-      <c r="AX14" s="12">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="AY14" s="12">
-        <v>0.11700000000000001</v>
-      </c>
-      <c r="AZ14" s="12">
-        <v>-2.11</v>
-      </c>
-      <c r="BA14" s="12">
-        <v>-2.11</v>
-      </c>
-      <c r="BB14" s="12">
-        <v>-1.8149999999999999</v>
-      </c>
-      <c r="BC14" s="12">
-        <v>-1.0389999999999999</v>
-      </c>
-      <c r="BD14" s="12">
-        <v>-2.0249999999999999</v>
-      </c>
-      <c r="BE14" s="12">
-        <v>-1.6060000000000001</v>
-      </c>
-      <c r="BH14" s="12">
-        <v>-1.343</v>
-      </c>
-      <c r="BI14" s="12">
-        <v>-1.343</v>
-      </c>
-      <c r="BJ14" s="12">
-        <v>-4.8</v>
-      </c>
-      <c r="BK14" s="12">
-        <v>-4.33</v>
+        <v>3.4500000000000003E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="21" t="s">
         <v>71</v>
       </c>
@@ -2711,378 +2573,510 @@
         <v>63</v>
       </c>
       <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="12">
+        <v>-5.0199999999999996</v>
+      </c>
+      <c r="F15" s="12">
+        <v>-5.78</v>
+      </c>
+      <c r="G15" s="12">
+        <v>-5.32</v>
+      </c>
+      <c r="H15" s="12">
+        <v>-5.32</v>
+      </c>
+      <c r="I15" s="12">
+        <v>-2.99</v>
+      </c>
+      <c r="J15" s="12">
+        <v>-2.99</v>
+      </c>
+      <c r="K15" s="12">
+        <v>-5.3</v>
+      </c>
+      <c r="L15" s="12">
+        <v>-5.3</v>
+      </c>
+      <c r="N15" s="12">
+        <v>-1.75</v>
+      </c>
+      <c r="O15" s="12">
+        <v>-1.75</v>
+      </c>
+      <c r="P15" s="12">
+        <v>-4.49</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>-2.8159999999999998</v>
+      </c>
+      <c r="R15" s="12">
+        <v>-2.8159999999999998</v>
+      </c>
+      <c r="S15" s="12">
+        <v>-4.34</v>
+      </c>
+      <c r="T15" s="12">
+        <v>-4.34</v>
+      </c>
+      <c r="U15" s="12">
+        <v>-1.8460000000000001</v>
+      </c>
+      <c r="V15" s="12">
+        <v>-1.8460000000000001</v>
+      </c>
+      <c r="W15" s="12">
+        <v>-5.68</v>
+      </c>
+      <c r="X15" s="12">
+        <v>-2.97</v>
+      </c>
+      <c r="Y15" s="12">
+        <v>-6.15</v>
+      </c>
+      <c r="Z15" s="12">
+        <v>-3.95</v>
+      </c>
+      <c r="AA15" s="12">
+        <v>-6.32</v>
+      </c>
+      <c r="AB15" s="12">
+        <v>-3.81</v>
+      </c>
+      <c r="AC15" s="12">
+        <v>-5.71</v>
+      </c>
+      <c r="AD15" s="12">
+        <v>-2.86</v>
+      </c>
+      <c r="AE15" s="12">
+        <v>0.79</v>
+      </c>
+      <c r="AF15" s="12">
+        <v>-5.14</v>
+      </c>
+      <c r="AG15" s="12">
+        <v>-5.14</v>
+      </c>
+      <c r="AH15" s="12">
+        <v>-3.46</v>
+      </c>
+      <c r="AI15" s="12">
+        <v>-3.31</v>
+      </c>
+      <c r="AK15" s="12">
+        <v>-2.7280000000000002</v>
+      </c>
+      <c r="AL15" s="12">
+        <v>-2.7280000000000002</v>
+      </c>
+      <c r="AM15" s="12">
+        <v>-4</v>
+      </c>
+      <c r="AN15" s="12">
+        <v>-4</v>
+      </c>
+      <c r="AO15" s="12">
+        <v>-5.5</v>
+      </c>
+      <c r="AP15" s="12">
+        <v>-5.5</v>
+      </c>
+      <c r="AQ15" s="12">
+        <v>-6.11</v>
+      </c>
+      <c r="AR15" s="12">
+        <v>-6.11</v>
+      </c>
+      <c r="AS15" s="12">
+        <v>-2.3029999999999999</v>
+      </c>
+      <c r="AT15" s="12">
+        <v>-2.3029999999999999</v>
+      </c>
+      <c r="AU15" s="12">
+        <v>-1.9</v>
+      </c>
+      <c r="AV15" s="12">
+        <v>-1.9</v>
+      </c>
+      <c r="AX15" s="12">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="AY15" s="12">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="AZ15" s="12">
+        <v>-2.11</v>
+      </c>
+      <c r="BA15" s="12">
+        <v>-2.11</v>
+      </c>
+      <c r="BB15" s="12">
+        <v>-1.8149999999999999</v>
+      </c>
+      <c r="BC15" s="12">
+        <v>-1.0389999999999999</v>
+      </c>
+      <c r="BD15" s="12">
+        <v>-2.0249999999999999</v>
+      </c>
+      <c r="BE15" s="12">
+        <v>-1.6060000000000001</v>
+      </c>
+      <c r="BH15" s="12">
+        <v>-1.343</v>
+      </c>
+      <c r="BI15" s="12">
+        <v>-1.343</v>
+      </c>
+      <c r="BJ15" s="12">
+        <v>-4.8</v>
+      </c>
+      <c r="BK15" s="12">
+        <v>-4.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:76" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="7">
         <v>-1</v>
       </c>
-      <c r="BF15" s="12">
+      <c r="BF16" s="12">
         <v>-60.7</v>
       </c>
-      <c r="BG15" s="12">
+      <c r="BG16" s="12">
         <v>-42.5</v>
       </c>
     </row>
-    <row r="16" spans="1:77" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="21" t="s">
+    <row r="17" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B17" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="7">
-        <v>1</v>
-      </c>
-      <c r="E16" s="12">
-        <v>-1.76</v>
-      </c>
-      <c r="F16" s="12">
-        <v>-2.29</v>
-      </c>
-      <c r="G16" s="12">
-        <v>-1.8</v>
-      </c>
-      <c r="H16" s="12">
-        <v>-1.8</v>
-      </c>
-      <c r="K16" s="12">
-        <v>-0.93</v>
-      </c>
-      <c r="L16" s="12">
-        <v>-0.93</v>
-      </c>
-      <c r="N16" s="12">
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="O16" s="12">
-        <v>-1.1499999999999999</v>
-      </c>
-      <c r="P16" s="12">
-        <v>-3.51</v>
-      </c>
-      <c r="S16" s="12">
-        <v>-1.46</v>
-      </c>
-      <c r="T16" s="12">
-        <v>-1.46</v>
-      </c>
-      <c r="AF16" s="12">
-        <v>-2.23</v>
-      </c>
-      <c r="AG16" s="12">
-        <v>-2.23</v>
-      </c>
-      <c r="AH16" s="12">
-        <v>-1.57</v>
-      </c>
-      <c r="AI16" s="12">
-        <v>-1.49</v>
-      </c>
-      <c r="AK16" s="12">
-        <v>-2.16</v>
-      </c>
-      <c r="AL16" s="12">
-        <v>-2.16</v>
-      </c>
-      <c r="AM16" s="12">
-        <v>-1.5</v>
-      </c>
-      <c r="AN16" s="12">
-        <v>-1.5</v>
-      </c>
-      <c r="AX16" s="12">
-        <v>0.622</v>
-      </c>
-      <c r="AY16" s="12">
-        <v>0.622</v>
-      </c>
-      <c r="BH16" s="12">
-        <v>-1.6140000000000001</v>
-      </c>
-      <c r="BI16" s="12">
-        <v>-1.6140000000000001</v>
-      </c>
-      <c r="BJ16" s="12">
-        <v>-1.24</v>
-      </c>
-      <c r="BK16" s="12">
-        <v>-2.1800000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="11"/>
       <c r="D17" s="7">
         <v>1</v>
       </c>
+      <c r="E17" s="12">
+        <v>-1.76</v>
+      </c>
+      <c r="F17" s="12">
+        <v>-2.29</v>
+      </c>
       <c r="G17" s="12">
-        <v>51.31</v>
-      </c>
-      <c r="J17" s="12">
-        <v>-74.7</v>
+        <v>-1.8</v>
+      </c>
+      <c r="H17" s="12">
+        <v>-1.8</v>
+      </c>
+      <c r="K17" s="12">
+        <v>-0.93</v>
       </c>
       <c r="L17" s="12">
-        <v>17</v>
+        <v>-0.93</v>
       </c>
       <c r="N17" s="12">
-        <v>-34.04</v>
-      </c>
-      <c r="Q17" s="12">
-        <v>-39.07</v>
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="O17" s="12">
+        <v>-1.1499999999999999</v>
+      </c>
+      <c r="P17" s="12">
+        <v>-3.51</v>
+      </c>
+      <c r="S17" s="12">
+        <v>-1.46</v>
       </c>
       <c r="T17" s="12">
-        <v>62.5</v>
-      </c>
-      <c r="U17" s="12">
-        <v>61.503</v>
+        <v>-1.46</v>
       </c>
       <c r="AF17" s="12">
-        <v>-160.27000000000001</v>
+        <v>-2.23</v>
+      </c>
+      <c r="AG17" s="12">
+        <v>-2.23</v>
+      </c>
+      <c r="AH17" s="12">
+        <v>-1.57</v>
+      </c>
+      <c r="AI17" s="12">
+        <v>-1.49</v>
       </c>
       <c r="AK17" s="12">
-        <v>56.386000000000003</v>
+        <v>-2.16</v>
+      </c>
+      <c r="AL17" s="12">
+        <v>-2.16</v>
       </c>
       <c r="AM17" s="12">
-        <v>-30</v>
-      </c>
-      <c r="AP17" s="12">
-        <v>56.3</v>
-      </c>
-      <c r="AR17" s="12">
-        <v>48.87</v>
-      </c>
-      <c r="AS17" s="12">
-        <v>36.648000000000003</v>
-      </c>
-      <c r="AV17" s="12">
-        <v>78.06</v>
+        <v>-1.5</v>
+      </c>
+      <c r="AN17" s="12">
+        <v>-1.5</v>
+      </c>
+      <c r="AX17" s="12">
+        <v>0.622</v>
       </c>
       <c r="AY17" s="12">
-        <v>-63.343000000000004</v>
-      </c>
-      <c r="BA17" s="12">
-        <v>45.323</v>
-      </c>
-      <c r="BD17" s="12">
-        <v>54.735999999999997</v>
-      </c>
-      <c r="BE17" s="12">
-        <v>58.36</v>
-      </c>
-      <c r="BF17" s="12">
-        <v>50.6</v>
-      </c>
-      <c r="BG17" s="12">
-        <v>46.2</v>
+        <v>0.622</v>
       </c>
       <c r="BH17" s="12">
-        <v>27.463000000000001</v>
+        <v>-1.6140000000000001</v>
+      </c>
+      <c r="BI17" s="12">
+        <v>-1.6140000000000001</v>
+      </c>
+      <c r="BJ17" s="12">
+        <v>-1.24</v>
+      </c>
+      <c r="BK17" s="12">
+        <v>-2.1800000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>65</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="C18" s="11"/>
       <c r="D18" s="7">
         <v>1</v>
       </c>
-      <c r="P18" s="12">
-        <v>5.5</v>
-      </c>
-      <c r="Y18" s="12">
-        <v>2.12</v>
-      </c>
-      <c r="Z18" s="12">
-        <v>2.69</v>
-      </c>
-      <c r="AA18" s="12">
-        <v>2.69</v>
-      </c>
-      <c r="AB18" s="12">
-        <v>2.41</v>
+      <c r="G18" s="12">
+        <v>51.31</v>
+      </c>
+      <c r="J18" s="12">
+        <v>-74.7</v>
+      </c>
+      <c r="L18" s="12">
+        <v>17</v>
+      </c>
+      <c r="N18" s="12">
+        <v>-34.04</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>-39.07</v>
+      </c>
+      <c r="T18" s="12">
+        <v>62.5</v>
+      </c>
+      <c r="U18" s="12">
+        <v>61.503</v>
+      </c>
+      <c r="AF18" s="12">
+        <v>-160.27000000000001</v>
+      </c>
+      <c r="AK18" s="12">
+        <v>56.386000000000003</v>
       </c>
       <c r="AM18" s="12">
-        <v>3</v>
-      </c>
-      <c r="AN18" s="12">
-        <v>3</v>
+        <v>-30</v>
+      </c>
+      <c r="AP18" s="12">
+        <v>56.3</v>
+      </c>
+      <c r="AR18" s="12">
+        <v>48.87</v>
+      </c>
+      <c r="AS18" s="12">
+        <v>36.648000000000003</v>
+      </c>
+      <c r="AV18" s="12">
+        <v>78.06</v>
+      </c>
+      <c r="AY18" s="12">
+        <v>-63.343000000000004</v>
+      </c>
+      <c r="BA18" s="12">
+        <v>45.323</v>
+      </c>
+      <c r="BD18" s="12">
+        <v>54.735999999999997</v>
+      </c>
+      <c r="BE18" s="12">
+        <v>58.36</v>
+      </c>
+      <c r="BF18" s="12">
+        <v>50.6</v>
+      </c>
+      <c r="BG18" s="12">
+        <v>46.2</v>
       </c>
       <c r="BH18" s="12">
-        <v>4.3490000000000002</v>
-      </c>
-      <c r="BI18" s="12">
-        <v>4.3490000000000002</v>
+        <v>27.463000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D19" s="7">
         <v>1</v>
       </c>
-      <c r="AS19" s="12">
-        <v>1.365</v>
-      </c>
-      <c r="AT19" s="12">
-        <v>1.365</v>
-      </c>
-      <c r="BE19" s="12">
-        <v>0.89100000000000001</v>
+      <c r="P19" s="12">
+        <v>5.5</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>2.12</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>2.69</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>2.69</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>2.41</v>
+      </c>
+      <c r="AM19" s="12">
+        <v>3</v>
+      </c>
+      <c r="AN19" s="12">
+        <v>3</v>
+      </c>
+      <c r="BH19" s="12">
+        <v>4.3490000000000002</v>
+      </c>
+      <c r="BI19" s="12">
+        <v>4.3490000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="21" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" s="7">
         <v>1</v>
       </c>
-      <c r="BG20" s="12">
-        <v>0.65</v>
-      </c>
-      <c r="BH20" s="12">
-        <v>1.1910000000000001</v>
-      </c>
-      <c r="BI20" s="12">
-        <v>1.1910000000000001</v>
+      <c r="AS20" s="12">
+        <v>1.365</v>
+      </c>
+      <c r="AT20" s="12">
+        <v>1.365</v>
+      </c>
+      <c r="BE20" s="12">
+        <v>0.89100000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>118</v>
+        <v>81</v>
       </c>
       <c r="D21" s="7">
         <v>1</v>
       </c>
-      <c r="M21" s="12">
-        <v>23.29</v>
+      <c r="BG21" s="12">
+        <v>0.65</v>
+      </c>
+      <c r="BH21" s="12">
+        <v>1.1910000000000001</v>
+      </c>
+      <c r="BI21" s="12">
+        <v>1.1910000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="11"/>
+        <v>83</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>118</v>
+      </c>
       <c r="D22" s="7">
         <v>1</v>
       </c>
-      <c r="BG22" s="12">
-        <v>8.43</v>
+      <c r="M22" s="12">
+        <v>23.29</v>
       </c>
     </row>
-    <row r="23" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="7">
         <v>1</v>
       </c>
       <c r="BG23" s="12">
+        <v>8.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="7">
+        <v>1</v>
+      </c>
+      <c r="BG24" s="12">
         <v>16.100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="21" t="s">
+    <row r="25" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B25" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D25" s="7">
         <v>2</v>
       </c>
-      <c r="BF24" s="12">
+      <c r="BF25" s="12">
         <v>0.1</v>
       </c>
-      <c r="BG24" s="12">
+      <c r="BG25" s="12">
         <v>0.1</v>
       </c>
     </row>
-    <row r="25" spans="1:61" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="D25" s="7">
-        <v>1</v>
-      </c>
-      <c r="X25" s="12">
-        <v>-5.5</v>
-      </c>
-      <c r="Z25" s="12">
-        <v>-5.69</v>
-      </c>
-      <c r="AB25" s="12">
-        <v>-6.92</v>
-      </c>
-      <c r="AD25" s="12">
-        <v>-6.22</v>
-      </c>
-      <c r="AQ25" s="12">
-        <v>-4.87</v>
-      </c>
-      <c r="AR25" s="12">
-        <v>-4.87</v>
-      </c>
-      <c r="BD25" s="12">
-        <v>-4.3810000000000002</v>
-      </c>
-      <c r="BE25" s="12">
-        <v>-4.016</v>
-      </c>
-      <c r="BF25" s="12">
-        <v>-5.08</v>
-      </c>
-      <c r="BG25" s="12">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:63" s="12" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="20" t="s">
         <v>85</v>
       </c>
@@ -3093,9 +3087,53 @@
         <v>66</v>
       </c>
       <c r="D26" s="7">
+        <v>1</v>
+      </c>
+      <c r="X26" s="12">
+        <v>-5.5</v>
+      </c>
+      <c r="Z26" s="12">
+        <v>-5.69</v>
+      </c>
+      <c r="AB26" s="12">
+        <v>-6.92</v>
+      </c>
+      <c r="AD26" s="12">
+        <v>-6.22</v>
+      </c>
+      <c r="AQ26" s="12">
+        <v>-4.87</v>
+      </c>
+      <c r="AR26" s="12">
+        <v>-4.87</v>
+      </c>
+      <c r="BD26" s="12">
+        <v>-4.3810000000000002</v>
+      </c>
+      <c r="BE26" s="12">
+        <v>-4.016</v>
+      </c>
+      <c r="BF26" s="12">
+        <v>-5.08</v>
+      </c>
+      <c r="BG26" s="12">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:63" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="7">
         <v>2</v>
       </c>
-      <c r="AJ26" s="12">
+      <c r="AJ27" s="12">
         <v>-6.8000000000000005E-2</v>
       </c>
     </row>
